--- a/branches/migration/2026.0.3-template-v0.11.3/observations-summary.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="314">
   <si>
     <t>Profile</t>
   </si>
@@ -447,18 +447,6 @@
   </si>
   <si>
     <t>SNOMED CT#69536005</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-muv-zerebraler-perfusionsdruck</t>
-  </si>
-  <si>
-    <t>MII PR ICU MUV zerebraler Perfusionsdruck</t>
-  </si>
-  <si>
-    <t>null#250846007, null#61017-0, null#153604</t>
-  </si>
-  <si>
-    <t>SNOMED CT#263353005</t>
   </si>
   <si>
     <t>mii-pr-icu-parameter-von-extrakorporalen-verfahren</t>
@@ -1099,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2615,13 +2603,13 @@
         <v>146</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>16</v>
@@ -2636,7 +2624,7 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>14</v>
@@ -2644,28 +2632,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H45" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
@@ -2685,13 +2673,13 @@
         <v>152</v>
       </c>
       <c r="C46" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>16</v>
@@ -2714,28 +2702,28 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>157</v>
+        <v>14</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>19</v>
@@ -2752,7 +2740,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2770,7 +2758,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -2787,7 +2775,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>14</v>
@@ -2805,7 +2793,7 @@
         <v>14</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
@@ -2822,7 +2810,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2840,7 +2828,7 @@
         <v>14</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>19</v>
@@ -2854,28 +2842,28 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>19</v>
@@ -2889,19 +2877,19 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="C52" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>16</v>
@@ -2924,28 +2912,28 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -2954,7 +2942,7 @@
         <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>14</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54">
@@ -2962,7 +2950,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2980,7 +2968,7 @@
         <v>14</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>19</v>
@@ -2989,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
@@ -2997,60 +2985,60 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>19</v>
@@ -3059,33 +3047,33 @@
         <v>14</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>167</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -3102,7 +3090,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -3120,7 +3108,7 @@
         <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -3137,7 +3125,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -3155,7 +3143,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -3172,7 +3160,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>14</v>
@@ -3190,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -3207,7 +3195,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>14</v>
@@ -3225,7 +3213,7 @@
         <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
@@ -3242,7 +3230,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -3260,7 +3248,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>19</v>
@@ -3277,7 +3265,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -3295,7 +3283,7 @@
         <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>19</v>
@@ -3312,7 +3300,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -3330,7 +3318,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>19</v>
@@ -3344,28 +3332,28 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
@@ -3379,13 +3367,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="B66" t="s" s="2">
+      <c r="C66" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
@@ -3397,10 +3385,10 @@
         <v>16</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>19</v>
@@ -3414,13 +3402,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
@@ -3432,10 +3420,10 @@
         <v>16</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>19</v>
@@ -3449,28 +3437,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>19</v>
@@ -3487,7 +3475,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>14</v>
@@ -3496,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
@@ -3505,7 +3493,7 @@
         <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>19</v>
@@ -3522,17 +3510,17 @@
         <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="C70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="F70" t="s" s="2">
         <v>14</v>
       </c>
@@ -3540,7 +3528,7 @@
         <v>14</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>19</v>
@@ -3557,7 +3545,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>14</v>
@@ -3566,7 +3554,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>14</v>
@@ -3575,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>19</v>
@@ -3592,7 +3580,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>14</v>
@@ -3601,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>14</v>
@@ -3610,7 +3598,7 @@
         <v>14</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>19</v>
@@ -3627,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3636,7 +3624,7 @@
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>14</v>
@@ -3645,7 +3633,7 @@
         <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
@@ -3659,28 +3647,28 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>19</v>
@@ -3694,13 +3682,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="B75" t="s" s="2">
+      <c r="C75" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>14</v>
@@ -3712,7 +3700,7 @@
         <v>16</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>18</v>
@@ -3735,22 +3723,22 @@
         <v>193</v>
       </c>
       <c r="C76" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D76" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E76" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="F76" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>19</v>
@@ -3764,31 +3752,31 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="B77" t="s" s="2">
+      <c r="C77" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="C77" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="D77" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E77" t="s" s="2">
+      <c r="F77" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G77" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="F77" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="H77" t="s" s="2">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>14</v>
@@ -3805,7 +3793,7 @@
         <v>200</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>14</v>
@@ -3817,13 +3805,13 @@
         <v>16</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>14</v>
@@ -3834,28 +3822,28 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="B79" t="s" s="2">
+      <c r="C79" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="C79" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s" s="2">
+      <c r="F79" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="H79" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="F79" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>19</v>
@@ -3875,7 +3863,7 @@
         <v>207</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>14</v>
@@ -3887,10 +3875,10 @@
         <v>16</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>19</v>
@@ -3904,28 +3892,28 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="B81" t="s" s="2">
+      <c r="C81" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="C81" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="F81" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>19</v>
@@ -3939,34 +3927,34 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="B82" t="s" s="2">
+      <c r="C82" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E82" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="C82" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E82" t="s" s="2">
+      <c r="F82" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="F82" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>14</v>
@@ -3980,28 +3968,28 @@
         <v>217</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>14</v>
@@ -4009,13 +3997,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>14</v>
@@ -4024,7 +4012,7 @@
         <v>223</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>17</v>
@@ -4044,22 +4032,22 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="B85" t="s" s="2">
+      <c r="C85" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="C85" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D85" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="F85" t="s" s="2">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>17</v>
@@ -4079,19 +4067,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B86" t="s" s="2">
+      <c r="C86" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D86" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>16</v>
@@ -4114,19 +4102,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="B87" t="s" s="2">
+      <c r="C87" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D87" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E87" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>16</v>
@@ -4149,22 +4137,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="B88" t="s" s="2">
+      <c r="C88" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="C88" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D88" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s" s="2">
+      <c r="F88" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="F88" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>17</v>
@@ -4190,7 +4178,7 @@
         <v>238</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>14</v>
@@ -4199,7 +4187,7 @@
         <v>239</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>17</v>
@@ -4219,22 +4207,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="B90" t="s" s="2">
+      <c r="C90" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="C90" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D90" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="F90" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>17</v>
@@ -4254,22 +4242,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="B91" t="s" s="2">
+      <c r="C91" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="C91" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D91" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>246</v>
-      </c>
       <c r="F91" t="s" s="2">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>17</v>
@@ -4289,22 +4277,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="B92" t="s" s="2">
+      <c r="C92" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="C92" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D92" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="F92" t="s" s="2">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>17</v>
@@ -4324,22 +4312,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="B93" t="s" s="2">
+      <c r="C93" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="C93" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D93" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="F93" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>17</v>
@@ -4359,22 +4347,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="B94" t="s" s="2">
+      <c r="C94" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="C94" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="F94" t="s" s="2">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>17</v>
@@ -4394,13 +4382,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="B95" t="s" s="2">
+      <c r="C95" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>14</v>
@@ -4435,16 +4423,16 @@
         <v>260</v>
       </c>
       <c r="C96" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="D96" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="F96" t="s" s="2">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>17</v>
@@ -4464,22 +4452,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="B97" t="s" s="2">
+      <c r="C97" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="C97" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="F97" t="s" s="2">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>17</v>
@@ -4499,22 +4487,22 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="B98" t="s" s="2">
+      <c r="C98" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="C98" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="F98" t="s" s="2">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>17</v>
@@ -4534,22 +4522,22 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="B99" t="s" s="2">
+      <c r="C99" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="C99" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D99" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E99" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="F99" t="s" s="2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>17</v>
@@ -4569,22 +4557,22 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="B100" t="s" s="2">
+      <c r="C100" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E100" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="C100" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="F100" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>17</v>
@@ -4604,22 +4592,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="B101" t="s" s="2">
+      <c r="C101" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="C101" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D101" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="F101" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>17</v>
@@ -4639,22 +4627,22 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="B102" t="s" s="2">
+      <c r="C102" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="C102" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D102" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s" s="2">
+      <c r="F102" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="F102" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>17</v>
@@ -4680,7 +4668,7 @@
         <v>282</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>14</v>
@@ -4689,7 +4677,7 @@
         <v>283</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>17</v>
@@ -4709,19 +4697,19 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="B104" t="s" s="2">
+      <c r="C104" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D104" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>16</v>
@@ -4744,19 +4732,19 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="B105" t="s" s="2">
+      <c r="C105" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D105" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E105" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>16</v>
@@ -4779,19 +4767,19 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="B106" t="s" s="2">
+      <c r="C106" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>16</v>
@@ -4814,19 +4802,19 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="B107" t="s" s="2">
+      <c r="C107" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D107" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>16</v>
@@ -4849,22 +4837,22 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="B108" t="s" s="2">
+      <c r="C108" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="C108" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="F108" t="s" s="2">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>17</v>
@@ -4884,22 +4872,22 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="B109" t="s" s="2">
+      <c r="C109" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="C109" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="F109" t="s" s="2">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>17</v>
@@ -4919,22 +4907,22 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="B110" t="s" s="2">
+      <c r="C110" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="C110" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D110" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E110" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="F110" t="s" s="2">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>17</v>
@@ -4954,22 +4942,22 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="B111" t="s" s="2">
+      <c r="C111" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="C111" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D111" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="F111" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>17</v>
@@ -4989,22 +4977,22 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="B112" t="s" s="2">
+      <c r="C112" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="C112" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>311</v>
-      </c>
       <c r="F112" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>17</v>
@@ -5024,22 +5012,22 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="B113" t="s" s="2">
+      <c r="C113" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="C113" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D113" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E113" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="F113" t="s" s="2">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>17</v>
@@ -5054,41 +5042,6 @@
         <v>14</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D114" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E114" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="F114" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K114" t="s" s="2">
         <v>14</v>
       </c>
     </row>
